--- a/report_cards/Report_Card_Daniel_Deborah.xlsx
+++ b/report_cards/Report_Card_Daniel_Deborah.xlsx
@@ -1259,7 +1259,7 @@
       </c>
       <c r="M20" s="39" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="N20" s="30" t="n"/>
@@ -1595,7 +1595,7 @@
       <c r="O29" s="36" t="n"/>
       <c r="P29" s="42" t="inlineStr">
         <is>
-          <t>9th</t>
+          <t>10th</t>
         </is>
       </c>
       <c r="Q29" s="35" t="n"/>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="X42" s="43" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="Y42" s="30" t="n"/>
@@ -2583,7 +2583,7 @@
       <c r="F52" s="36" t="n"/>
       <c r="G52" s="44" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="H52" s="35" t="n"/>

--- a/report_cards/Report_Card_Daniel_Deborah.xlsx
+++ b/report_cards/Report_Card_Daniel_Deborah.xlsx
@@ -1259,7 +1259,7 @@
       </c>
       <c r="M20" s="39" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>5th</t>
         </is>
       </c>
       <c r="N20" s="30" t="n"/>
@@ -1534,7 +1534,7 @@
       <c r="O28" s="36" t="n"/>
       <c r="P28" s="42" t="inlineStr">
         <is>
-          <t>7th</t>
+          <t>8th</t>
         </is>
       </c>
       <c r="Q28" s="35" t="n"/>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="X42" s="43" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>5th</t>
         </is>
       </c>
       <c r="Y42" s="30" t="n"/>
@@ -2379,7 +2379,7 @@
       <c r="O46" s="36" t="n"/>
       <c r="P46" s="42" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="Q46" s="35" t="n"/>
@@ -2583,7 +2583,7 @@
       <c r="F52" s="36" t="n"/>
       <c r="G52" s="44" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>5th</t>
         </is>
       </c>
       <c r="H52" s="35" t="n"/>

--- a/report_cards/Report_Card_Daniel_Deborah.xlsx
+++ b/report_cards/Report_Card_Daniel_Deborah.xlsx
@@ -1259,7 +1259,7 @@
       </c>
       <c r="M20" s="39" t="inlineStr">
         <is>
-          <t>5th</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="N20" s="30" t="n"/>
@@ -1890,16 +1890,32 @@
       <c r="D35" s="35" t="n"/>
       <c r="E35" s="35" t="n"/>
       <c r="F35" s="36" t="n"/>
-      <c r="G35" s="18" t="inlineStr"/>
-      <c r="H35" s="18" t="inlineStr"/>
+      <c r="G35" s="42" t="n">
+        <v>15</v>
+      </c>
+      <c r="H35" s="42" t="n">
+        <v>23</v>
+      </c>
       <c r="I35" s="36" t="n"/>
-      <c r="J35" s="18" t="inlineStr"/>
+      <c r="J35" s="42" t="n">
+        <v>0</v>
+      </c>
       <c r="K35" s="36" t="n"/>
-      <c r="L35" s="18" t="inlineStr"/>
+      <c r="L35" s="18">
+        <f>SUM(G35, H35, J35)</f>
+        <v/>
+      </c>
       <c r="M35" s="36" t="n"/>
-      <c r="N35" s="18" t="inlineStr"/>
+      <c r="N35" s="18">
+        <f>IF(L35&gt;=75,"A1",IF(L35&gt;=70,"B2",IF(L35&gt;=65,"B3",IF(L35&gt;=60,"C4",IF(L35&gt;=55,"C5",IF(L35&gt;=50,"C6",IF(L35&gt;=45,"D7",IF(L35&gt;=40,"E8","F9"))))))))</f>
+        <v/>
+      </c>
       <c r="O35" s="36" t="n"/>
-      <c r="P35" s="18" t="inlineStr"/>
+      <c r="P35" s="42" t="inlineStr">
+        <is>
+          <t>7th</t>
+        </is>
+      </c>
       <c r="Q35" s="35" t="n"/>
       <c r="R35" s="36" t="n"/>
       <c r="T35" s="18" t="inlineStr">
@@ -2032,7 +2048,7 @@
         </is>
       </c>
       <c r="X38" s="43" t="n">
-        <v>712</v>
+        <v>750</v>
       </c>
       <c r="Y38" s="30" t="n"/>
       <c r="Z38" s="30" t="n"/>
@@ -2084,7 +2100,7 @@
         </is>
       </c>
       <c r="X39" s="43" t="n">
-        <v>71.2</v>
+        <v>68.2</v>
       </c>
       <c r="Y39" s="30" t="n"/>
       <c r="Z39" s="30" t="n"/>
@@ -2121,7 +2137,7 @@
       </c>
       <c r="X40" s="43" t="inlineStr">
         <is>
-          <t>71.2%</t>
+          <t>68.18%</t>
         </is>
       </c>
       <c r="Y40" s="30" t="n"/>
@@ -2159,7 +2175,7 @@
       </c>
       <c r="X41" s="43" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>B3</t>
         </is>
       </c>
       <c r="Y41" s="30" t="n"/>
@@ -2213,7 +2229,7 @@
       </c>
       <c r="X42" s="43" t="inlineStr">
         <is>
-          <t>5th</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="Y42" s="30" t="n"/>
@@ -2338,7 +2354,7 @@
         </is>
       </c>
       <c r="X45" s="43" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="Y45" s="30" t="n"/>
       <c r="Z45" s="30" t="n"/>
@@ -2450,7 +2466,7 @@
       <c r="E48" s="35" t="n"/>
       <c r="F48" s="36" t="n"/>
       <c r="G48" s="44" t="n">
-        <v>712</v>
+        <v>750</v>
       </c>
       <c r="H48" s="35" t="n"/>
       <c r="I48" s="35" t="n"/>
@@ -2482,7 +2498,7 @@
       <c r="E49" s="35" t="n"/>
       <c r="F49" s="36" t="n"/>
       <c r="G49" s="44" t="n">
-        <v>71.2</v>
+        <v>68.2</v>
       </c>
       <c r="H49" s="35" t="n"/>
       <c r="I49" s="35" t="n"/>
@@ -2515,7 +2531,7 @@
       <c r="F50" s="36" t="n"/>
       <c r="G50" s="44" t="inlineStr">
         <is>
-          <t>71.2%</t>
+          <t>68.18%</t>
         </is>
       </c>
       <c r="H50" s="35" t="n"/>
@@ -2549,7 +2565,7 @@
       <c r="F51" s="36" t="n"/>
       <c r="G51" s="44" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>B3</t>
         </is>
       </c>
       <c r="H51" s="35" t="n"/>
@@ -2583,7 +2599,7 @@
       <c r="F52" s="36" t="n"/>
       <c r="G52" s="44" t="inlineStr">
         <is>
-          <t>5th</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="H52" s="35" t="n"/>
@@ -2662,7 +2678,7 @@
       <c r="E55" s="35" t="n"/>
       <c r="F55" s="36" t="n"/>
       <c r="G55" s="44" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="H55" s="35" t="n"/>
       <c r="I55" s="35" t="n"/>

--- a/report_cards/Report_Card_Daniel_Deborah.xlsx
+++ b/report_cards/Report_Card_Daniel_Deborah.xlsx
@@ -1259,7 +1259,7 @@
       </c>
       <c r="M20" s="39" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="N20" s="30" t="n"/>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="X42" s="43" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="Y42" s="30" t="n"/>
@@ -2271,7 +2271,7 @@
       <c r="O43" s="36" t="n"/>
       <c r="P43" s="42" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="Q43" s="35" t="n"/>
@@ -2599,7 +2599,7 @@
       <c r="F52" s="36" t="n"/>
       <c r="G52" s="44" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="H52" s="35" t="n"/>

--- a/report_cards/Report_Card_Daniel_Deborah.xlsx
+++ b/report_cards/Report_Card_Daniel_Deborah.xlsx
@@ -1891,14 +1891,14 @@
       <c r="E35" s="35" t="n"/>
       <c r="F35" s="36" t="n"/>
       <c r="G35" s="42" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="H35" s="42" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="I35" s="36" t="n"/>
       <c r="J35" s="42" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="K35" s="36" t="n"/>
       <c r="L35" s="18">
@@ -2271,7 +2271,7 @@
       <c r="O43" s="36" t="n"/>
       <c r="P43" s="42" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="Q43" s="35" t="n"/>
